--- a/피지컬팀 프로젝트 mk2.xlsx
+++ b/피지컬팀 프로젝트 mk2.xlsx
@@ -2477,7 +2477,7 @@
     <t>계측 데이터 전달(평시)</t>
   </si>
   <si>
-    <t>센서노드(라즈베리파이)에 상시 상주하는 기본 수집 컨테이너가 계측값을 구역 엣지노드로 저주기 전달한다. 단, 라즈베리파이는 센서 값을 최대 속도로 상시 수집하고 있으므로(HW-S-01) 임계값 초과·급변(변화율 초과)은 로컬에서 즉시 감지하여 보고 주기와 무관하게 이벤트 메시지를 즉시 발행한다(report-by-exception, SCADA 표준 패턴). 즉 1분 주기는 '정상 범위' 정기 확인용이고, 위험 징후 감지는 주기에 얹히지 않아 지연이 없다. 기본 컨테이너는 하트비트(HW-S-06)와 함께 항상 유지된다(고주기 연속 보고는 HW-S-03의 별도 컨테이너가 담당).</t>
+    <t>센서노드(라즈베리파이)에 상시 상주하는 기본 수집 컨테이너가 계측값을 구역 엣지노드로 저주기 전달한다. 단, 라즈베리파이는 센서 값을 최대 속도로 상시 수집하고 있으므로(HW-S-01) 임계값 초과·급변(변화율 초과)은 로컬에서 즉시 감지하여 보고 주기와 무관하게 이벤트 메시지를 즉시 발행한다(report-by-exception, SCADA 표준 패턴). 즉 1분 주기는 '정상 범위' 정기 확인용이고, 위험 징후 감지는 주기에 얹히지 않아 지연이 없다. 기본 컨테이너는 하트비트(HW-S-05)와 함께 항상 유지된다(고주기 연속 보고로의 전환은 HW-S-03이 담당).</t>
   </si>
   <si>
     <t>라즈베리파이→엣지노드</t>
@@ -2499,7 +2499,7 @@
     <t>이벤트 모드 고주기 보고</t>
   </si>
   <si>
-    <t>강우 감지·수위 임계값 초과 등 이벤트 발생 시, 엣지노드의 쿠버네티스가 센서노드에 고주기 모니터링 컨테이너를 배포하여 1초 주기 보고로 전환한다. 홍수 등 재난 상황에서는 대응 골든타임이 존재하므로, 상황 발생 시 실시간성에 준하는 데이터 갱신이 필요하여 정의한다. 상황 종료 시 해당 컨테이너는 제거되어 평시(기본 컨테이너 저주기 보고)로 복귀한다.</t>
+    <t>강우 감지·수위 임계값 초과 등 이벤트 발생 시 1초 주기 보고로 전환한다. 전환은 ①센서노드가 임계·급변을 로컬에서 판정해 즉시 자율 전환하는 것을 주 경로로 하고, ②엣지노드의 주기 전환 명령(HW-S-04)을 구역 단위 일관성 확보를 위한 원격 오버라이드로 둔다. K3s agent는 엣지 제어평면에 연결되지 못하면 컨테이너를 기동조차 하지 못하고(k3s-io/k3s#1686) 이미지 pull이 필요하면 기동에 30~60초가 걸리므로, 링크가 가장 불안정한 재난 시점의 주기 전환을 컨테이너 배포에 의존시키지 않는다. 홍수 등 재난 상황에서는 대응 골든타임이 존재하므로, 상황 발생 시 실시간성에 준하는 데이터 갱신이 필요하여 정의한다. 상황 종료 시 평시 저주기 보고로 복귀한다.</t>
   </si>
   <si>
     <t>이벤트 발생 시 1초 1회 (1 Hz)</t>
@@ -2521,7 +2521,7 @@
     <t>적응형 주기 전환 명령 수신</t>
   </si>
   <si>
-    <t>엣지노드가 상황 판단(강우 시작·종료 등)에 따라 센서노드의 모니터링 모드를 전환한다. 전환의 실체는 쿠버네티스를 통한 컨테이너 배포/제거이다: 강우 시작 시 고주기 모니터링 컨테이너를 배포하고, 종료 시 제거하여 평시로 복귀한다. 평시↔이벤트 모드 전환을 센서 단독 판단이 아닌 엣지노드 주도로 제어하여 구역 단위 일관성을 확보하기 위해 정의한다.</t>
+    <t>엣지노드가 상황 판단(강우 시작·종료 등)에 따라 센서노드의 모니터링 모드를 전환한다. 전환 명령은 MQTT 제어 채널로 하달하며 HW-C-06의 ACK·수행 결과 체계를 따른다. 컨테이너 배포/제거(HW-C-03)는 AI 추론·영상 분석 등 증강 기능의 기동/종료에 사용하며 보고 주기 전환의 실체로는 사용하지 않는다. 평시↔이벤트 모드 전환을 센서 단독 판단이 아닌 엣지노드 주도로 제어하여 구역 단위 일관성을 확보하기 위해 정의한다.</t>
   </si>
   <si>
     <t>엣지노드→라즈베리파이</t>
@@ -2685,7 +2685,7 @@
     <t>컨테이너 기반 구조(쿠버네티스 배포·제거)</t>
   </si>
   <si>
-    <t>장치 내 수집·보고·모니터링 기능은 기능 단위의 도커 컨테이너로 패키징하고, 구역 엣지노드의 쿠버네티스(라즈베리파이 환경 특성상 경량판 K3s)가 센서노드·로봇 온보드 라즈베리파이를 워커 노드로 편입하여 상황에 따라 컨테이너를 배포(기동)/제거(종료)한다. 예: 수위 고주기 모니터링 컨테이너는 강우 시작 시 배포되고 강우 종료 시 내려간다. 필요 시에만 컨테이너를 띄워 저사양 장치의 자원을 절약하고, 기능별 장애 격리와 비정상 종료 시 자동 재기동(쿠버네티스 셀프힐링)을 확보하기 위해 정의한다.</t>
+    <t>장치 내 수집·보고·모니터링 기능은 기능 단위의 도커 컨테이너로 패키징하고, 구역 엣지노드의 쿠버네티스(라즈베리파이 환경 특성상 경량판 K3s)가 센서노드·로봇 온보드 라즈베리파이를 워커 노드로 편입하여 상황에 따라 컨테이너를 배포(기동)/제거(종료)한다. 예: 강우 시작 시 영상 분석·온디바이스 AI 추론 등 증강 기능 컨테이너가 배포되고 상황 종료 시 내려간다. 단 보고 주기 전환 자체는 상주 프로세스가 담당한다(HW-S-03). 필요 시에만 컨테이너를 띄워 저사양 장치의 자원을 절약하고, 기능별 장애 격리와 비정상 종료 시 자동 재기동(쿠버네티스 셀프힐링)을 확보하기 위해 정의한다.</t>
   </si>
   <si>
     <t>엣지노드→하드웨어 장치</t>

--- a/피지컬팀 프로젝트 mk2.xlsx
+++ b/피지컬팀 프로젝트 mk2.xlsx
@@ -188,7 +188,7 @@
     <t>프레임 참조·시간 동기 규약</t>
   </si>
   <si>
-    <t>대기 중 1초 1회(임무 중에는 상태 데이터가 겸함)</t>
+    <t>대기 중 5초 1회(임무 중에는 상태 데이터가 겸함)</t>
   </si>
   <si>
     <t>환경·보정 설정 적용</t>
@@ -1716,7 +1716,7 @@
     <t>현재 아키텍처에서 K3s 제어 기능은 구역 엣지에 위치한다. 어떤 말단이나 엣지 프로세스가 실제 worker가 되는지는 배포 구성으로 결정하고 요구사항에서 특정 하드웨어를 고정하지 않는다. 참고: 프로젝트 문서 data_transport_architecture_v2.docx §3.</t>
   </si>
   <si>
-    <t>임무 수행 중 50 ms (20 Hz) / 대기 중 1초 1회</t>
+    <t>임무 수행 중 50 ms (20 Hz) / 대기 중 5초 1회</t>
   </si>
   <si>
     <t>계획 승인 및 근거 표시</t>
@@ -2547,7 +2547,7 @@
     <t>센서를 담당하는 라즈베리파이(항상 켜져 있는 상시 노드)가 자신의 생존 상태를 엣지노드로 주기 전송한다. 하트비트는 노드(라즈베리파이) 수준의 생존 확인용이며, 노드 위에서 올렸다 내렸다 하는 개별 기능(계측·보고 컨테이너)의 생존은 엣지노드의 쿠버네티스가 liveness probe·파드 상태로 감시하고 비정상 종료 시 자동 재기동한다. 센서 값이 오지 않는 상황이 '센서 값 무변화'인지 '노드 장애'인지 '컨테이너 장애'인지 구분하기 위해 계측 데이터와 별도 채널의 생존 확인이 필요하여 정의한다.</t>
   </si>
   <si>
-    <t>1초 1회 (1 Hz)</t>
+    <t>5초 1회</t>
   </si>
   <si>
     <t>센서노드 생존 확인은 로봇/무인체계 통신에서 실제 사용되는 1 Hz 사례에 맞춘다. MAVLink 공식 문서는 RF telemetry 링크에서 HEARTBEAT를 일반적으로 1 Hz로 송신한다고 명시한다. 따라서 1초 하트비트를 초기 기준으로 사용하고 단절 판정은 HW-S-07에서 별도로 정의한다.
@@ -2594,7 +2594,7 @@
     <t>엣지노드→메인서버</t>
   </si>
   <si>
-    <t>1 Hz 하트비트 기준 4회 연속 미수신(약 4초) 후 즉시 오프라인 반영</t>
+    <t>하트비트 4회 연속 미수신(약 20초) 후 오프라인 반영. 실제 급사·링크 두절은 MQTT 유언 메시지(LWT)가 더 빨리 잡는다 — 프로세스 급사는 즉시, 침묵형 링크 끊김은 keepalive 기준 약 15초(실측)</t>
   </si>
   <si>
     <t>HW-S-05의 1 Hz heartbeat를 기준으로 단절 판정도 공개 운용 사례와 일치시킨다. MAVLink 공식 문서는 RF telemetry에서 1 Hz heartbeat를 일반적으로 사용하고 4~5개의 예상 메시지를 받지 못하면 연결 해제로 판단하는 사례를 설명한다. 본 요구사항은 그 범위의 빠른 쪽인 4회 미수신(약 4초)을 채택하고, 판정 뒤 서버 반영은 즉시 수행한다.
@@ -2748,7 +2748,7 @@
     <t>백엔드가 대상·기간·조작자·발행 경로로 감사를 필터 조회하는 API를 제공해, "이 대상을 마지막으로 조작한 사람"과 판단 근거를 확인할 수 있게 해야 한다. 가시화 클라이언트는 감사 저장소에 직접 접근하지 않고 이 API를 경유한다.</t>
   </si>
   <si>
-    <t>OpenTelemetry metrics export 60초 1회</t>
+    <t>OpenTelemetry metrics export 15초 1회</t>
   </si>
   <si>
     <t>중요 오류나 이상 판단은 당시 사용한 원본 입력, 실행 구성, 버전과 사용 가능한 업무 데이터·관측 참조를 연결해 다시 분석할 수 있어야 한다. 업무·책임 추적과 기술 성능 추적은 서로 다른 목적으로 유지해야 한다. 업무 스트림이 단기 보존 구간 안에 있는 경우에는 전송 로그의 위치를 이용해 재현할 수 있고, 보존 기간이 지난 데이터는 업무 저장소나 별도 아카이브가 존재하는 경우 그 참조를 사용해야 한다. 특정 전송·관측 기술이 없더라도 확보된 참조 범위에서 재현 정보를 남겨야 한다.</t>
@@ -3247,7 +3247,7 @@
     <t>AI/백엔드 → 가시화(계획·근거) → (승인) → 백엔드 → 엣지·로봇</t>
   </si>
   <si>
-    <t>제어노드 하트비트 1초 1회 / 4회 연속 미수신(약 4초) 시 통신 장애 판정 / 복구 시 즉시 재동기화</t>
+    <t>제어노드 하트비트 5초 1회 / 4회 연속 미수신(약 20초) 시 통신 장애 판정. 단 세션 단절(LWT)이 먼저 잡히면 그 시점부터 4초 내 잠금 / 복구 시 즉시 재동기화</t>
   </si>
   <si>
     <t>VZ-D-02</t>
